--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1448,6 +1448,145 @@
       <c r="K16" s="0" t="inlineStr"/>
       <c r="L16" s="0" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ItemTargetKind</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>主动道具目标类型：决定作用对象与可用情境</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>无目标(全局/整体行为)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>BoardDish</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>棋盘上的菜(本局临时,仅战斗)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>RecipeDish</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>菜谱里的菜(永久,任意情境含战斗)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>StomachCell</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>胃碎片格</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CellTag</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>格子标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>FlavorSlot</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>某道菜的风味槽</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>无目标(全局资源/节奏,时间轴类限地图)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1449,139 +1449,154 @@
       <c r="L16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>OnAcquire</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>获得时结算一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>ItemTargetKind</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>主动道具目标类型：决定作用对象与可用情境</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>无目标(全局/整体行为)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="H18" t="inlineStr">
+    <row r="19">
+      <c r="H19" s="0" t="inlineStr">
         <is>
           <t>BoardDish</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>棋盘上的菜(本局临时,仅战斗)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="H19" t="inlineStr">
+    <row r="20">
+      <c r="H20" s="0" t="inlineStr">
         <is>
           <t>RecipeDish</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>菜谱里的菜(永久,任意情境含战斗)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="H20" t="inlineStr">
+    <row r="21">
+      <c r="H21" s="0" t="inlineStr">
         <is>
           <t>StomachCell</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>胃碎片格</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="H21" t="inlineStr">
+    <row r="22">
+      <c r="H22" s="0" t="inlineStr">
         <is>
           <t>CellTag</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>格子标签</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="H22" t="inlineStr">
+    <row r="23">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>FlavorSlot</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t>某道菜的风味槽</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="H23" t="inlineStr">
+    <row r="24">
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t>无目标(全局资源/节奏,时间轴类限地图)</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1313,10 +1313,9 @@
       <c r="L10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="0" t="inlineStr"/>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>ItemTriggerTiming</t>
+          <t>ItemTargetKind</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -1329,274 +1328,124 @@
           <t>False</t>
         </is>
       </c>
-      <c r="E11" s="0" t="inlineStr"/>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>道具触发时机</t>
-        </is>
-      </c>
-      <c r="G11" s="0" t="inlineStr"/>
+          <t>主动道具目标类型：决定作用对象与可用情境</t>
+        </is>
+      </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="I11" s="0" t="inlineStr"/>
-      <c r="J11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="0" t="inlineStr"/>
-      <c r="L11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>无目标(全局/整体行为)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="inlineStr"/>
-      <c r="B12" s="0" t="inlineStr"/>
-      <c r="C12" s="0" t="inlineStr"/>
-      <c r="D12" s="0" t="inlineStr"/>
-      <c r="E12" s="0" t="inlineStr"/>
-      <c r="F12" s="0" t="inlineStr"/>
-      <c r="G12" s="0" t="inlineStr"/>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>BeforeServe</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr"/>
-      <c r="J12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="0" t="inlineStr"/>
-      <c r="L12" s="0" t="inlineStr"/>
+          <t>BoardDish</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>棋盘上的菜(本局临时,仅战斗)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0" t="inlineStr"/>
-      <c r="B13" s="0" t="inlineStr"/>
-      <c r="C13" s="0" t="inlineStr"/>
-      <c r="D13" s="0" t="inlineStr"/>
-      <c r="E13" s="0" t="inlineStr"/>
-      <c r="F13" s="0" t="inlineStr"/>
-      <c r="G13" s="0" t="inlineStr"/>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>AfterServe</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr"/>
-      <c r="J13" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="0" t="inlineStr"/>
-      <c r="L13" s="0" t="inlineStr"/>
+          <t>RecipeDish</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>菜谱里的菜(永久,任意情境含战斗)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0" t="inlineStr"/>
-      <c r="B14" s="0" t="inlineStr"/>
-      <c r="C14" s="0" t="inlineStr"/>
-      <c r="D14" s="0" t="inlineStr"/>
-      <c r="E14" s="0" t="inlineStr"/>
-      <c r="F14" s="0" t="inlineStr"/>
-      <c r="G14" s="0" t="inlineStr"/>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>BeforeEat</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr"/>
-      <c r="J14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" s="0" t="inlineStr"/>
-      <c r="L14" s="0" t="inlineStr"/>
+          <t>StomachCell</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>胃碎片格</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0" t="inlineStr"/>
-      <c r="B15" s="0" t="inlineStr"/>
-      <c r="C15" s="0" t="inlineStr"/>
-      <c r="D15" s="0" t="inlineStr"/>
-      <c r="E15" s="0" t="inlineStr"/>
-      <c r="F15" s="0" t="inlineStr"/>
-      <c r="G15" s="0" t="inlineStr"/>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>AfterSettlement</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="inlineStr"/>
-      <c r="J15" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="0" t="inlineStr"/>
-      <c r="L15" s="0" t="inlineStr"/>
+          <t>CellTag</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>格子标签</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="inlineStr"/>
-      <c r="B16" s="0" t="inlineStr"/>
-      <c r="C16" s="0" t="inlineStr"/>
-      <c r="D16" s="0" t="inlineStr"/>
-      <c r="E16" s="0" t="inlineStr"/>
-      <c r="F16" s="0" t="inlineStr"/>
-      <c r="G16" s="0" t="inlineStr"/>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>RewardScreen</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr"/>
-      <c r="J16" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" s="0" t="inlineStr"/>
-      <c r="L16" s="0" t="inlineStr"/>
+          <t>FlavorSlot</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>某道菜的风味槽</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>OnAcquire</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>获得时结算一次</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>ItemTargetKind</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="F18" s="0" t="inlineStr">
-        <is>
-          <t>主动道具目标类型：决定作用对象与可用情境</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J18" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K18" s="0" t="inlineStr">
-        <is>
-          <t>无目标(全局/整体行为)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="H19" s="0" t="inlineStr">
-        <is>
-          <t>BoardDish</t>
-        </is>
-      </c>
-      <c r="J19" s="0" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="0" t="inlineStr">
-        <is>
-          <t>棋盘上的菜(本局临时,仅战斗)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>RecipeDish</t>
-        </is>
-      </c>
-      <c r="J20" s="0" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="0" t="inlineStr">
-        <is>
-          <t>菜谱里的菜(永久,任意情境含战斗)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>StomachCell</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="inlineStr">
-        <is>
-          <t>胃碎片格</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>CellTag</t>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="0" t="inlineStr">
-        <is>
-          <t>格子标签</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>FlavorSlot</t>
-        </is>
-      </c>
-      <c r="J23" s="0" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K23" s="0" t="inlineStr">
-        <is>
-          <t>某道菜的风味槽</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="H24" s="0" t="inlineStr">
+      <c r="H17" s="0" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="J24" s="0" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K24" s="0" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>无目标(全局资源/节奏,时间轴类限地图)</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -1352,7 +1352,7 @@
     <row r="12">
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>BoardDish</t>
+          <t>DiningTableDish</t>
         </is>
       </c>
       <c r="J12" s="0" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="K12" s="0" t="inlineStr">
         <is>
-          <t>棋盘上的菜(本局临时,仅战斗)</t>
+          <t>餐桌上的菜(本局临时,仅战斗)</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
     <row r="14">
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>StomachCell</t>
+          <t>DiningTableCell</t>
         </is>
       </c>
       <c r="J14" s="0" t="inlineStr">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="K14" s="0" t="inlineStr">
         <is>
-          <t>胃碎片格</t>
+          <t>餐桌格</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>CellTag</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="J15" s="0" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t>格子标签</t>
+          <t>材质</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1451,6 +1451,56 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ItemSpecialTag</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>道具特殊标签</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>负面道具</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2ab8e834cd114a74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8580b604162143be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -995,10 +995,8 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">道具类型：被动/主动</x:t>
-        </x:is>
+      <x:c r="F4" t="str">
+        <x:v>装饰品和消耗品类型：被动/主动</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>
@@ -1115,10 +1113,8 @@
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">道具品质</x:t>
-        </x:is>
+      <x:c r="F6" t="str">
+        <x:v>装饰品和消耗品品质</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr">
         <x:is>
@@ -1405,10 +1401,8 @@
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">主动道具目标类型：决定作用对象与可用情境</x:t>
-        </x:is>
+      <x:c r="F11" t="str">
+        <x:v>消耗品目标类型：决定作用对象与可用情境</x:v>
       </x:c>
       <x:c r="H11" t="inlineStr">
         <x:is>
@@ -1437,10 +1431,8 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="K12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">餐桌上的菜(本局临时,仅战斗)</x:t>
-        </x:is>
+      <x:c r="K12" t="str">
+        <x:v>餐桌上的菜(本局临时,仅经营挑战)</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1454,10 +1446,8 @@
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="K13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">菜谱里的菜(永久,任意情境含战斗)</x:t>
-        </x:is>
+      <x:c r="K13" t="str">
+        <x:v>食谱里的菜(永久,任意情境含经营挑战)</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1544,10 +1534,8 @@
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="F18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">道具特殊标签</x:t>
-        </x:is>
+      <x:c r="F18" t="str">
+        <x:v>装饰品和消耗品特殊标签</x:v>
       </x:c>
       <x:c r="H18" t="inlineStr">
         <x:is>
@@ -1572,10 +1560,8 @@
       <x:c r="J19" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">负面道具</x:t>
-        </x:is>
+      <x:c r="K19" t="str">
+        <x:v>诅咒装饰品</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1591,7 +1577,7 @@
       </x:c>
       <x:c r="E20"/>
       <x:c r="F20" t="str">
-        <x:v>主动道具分类</x:v>
+        <x:v>消耗品分类</x:v>
       </x:c>
       <x:c r="G20"/>
       <x:c r="H20" t="str">
@@ -1602,7 +1588,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>强化类主动道具</x:v>
+        <x:v>强化类消耗品</x:v>
       </x:c>
       <x:c r="L20"/>
     </x:row>
@@ -1622,7 +1608,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>调整类主动道具</x:v>
+        <x:v>调整类消耗品</x:v>
       </x:c>
       <x:c r="L21"/>
     </x:row>

--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8580b604162143be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd742810aad35435b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -996,7 +996,7 @@
         </x:is>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>装饰品和消耗品类型：被动/主动</x:v>
+        <x:v>装饰品和消耗品类型：装饰品/消耗品</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>

--- a/GourmetProject/GameConfig/Datas/__enums_item.xlsx
+++ b/GourmetProject/GameConfig/Datas/__enums_item.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd742810aad35435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ee4ed8ad7ce46fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1386,231 +1386,324 @@
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="B11" t="inlineStr">
+      <x:c r="A11"/>
+      <x:c r="B11"/>
+      <x:c r="C11"/>
+      <x:c r="D11"/>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11" t="str">
+        <x:v>Negative</x:v>
+      </x:c>
+      <x:c r="I11"/>
+      <x:c r="J11" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K11" t="str">
+        <x:v>诅咒品质</x:v>
+      </x:c>
+      <x:c r="L11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12"/>
+      <x:c r="B12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ItemTargetKind</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" t="inlineStr">
+      <x:c r="C12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" t="inlineStr">
+      <x:c r="D12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="F11" t="str">
+      <x:c r="E12"/>
+      <x:c r="F12" t="str">
         <x:v>消耗品目标类型：决定作用对象与可用情境</x:v>
       </x:c>
-      <x:c r="H11" t="inlineStr">
+      <x:c r="G12"/>
+      <x:c r="H12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="J11" t="inlineStr">
+      <x:c r="I12"/>
+      <x:c r="J12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">0</x:t>
         </x:is>
       </x:c>
-      <x:c r="K11" t="inlineStr">
+      <x:c r="K12" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">无目标(全局/整体行为)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="H12" t="inlineStr">
+      <x:c r="L12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">DiningTableDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="J12" t="inlineStr">
+      <x:c r="I13"/>
+      <x:c r="J13" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="K12" t="str">
+      <x:c r="K13" t="str">
         <x:v>餐桌上的菜(本局临时,仅经营挑战)</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="H13" t="inlineStr">
+      <x:c r="L13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">RecipeDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="J13" t="inlineStr">
+      <x:c r="I14"/>
+      <x:c r="J14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2</x:t>
         </x:is>
       </x:c>
-      <x:c r="K13" t="str">
+      <x:c r="K14" t="str">
         <x:v>食谱里的菜(永久,任意情境含经营挑战)</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="H14" t="inlineStr">
+      <x:c r="L14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">DiningTableCell</x:t>
         </x:is>
       </x:c>
-      <x:c r="J14" t="inlineStr">
+      <x:c r="I15"/>
+      <x:c r="J15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3</x:t>
         </x:is>
       </x:c>
-      <x:c r="K14" t="inlineStr">
+      <x:c r="K15" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">餐桌格</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="H15" t="inlineStr">
+      <x:c r="L15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16"/>
+      <x:c r="B16"/>
+      <x:c r="C16"/>
+      <x:c r="D16"/>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
+      <x:c r="G16"/>
+      <x:c r="H16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Material</x:t>
         </x:is>
       </x:c>
-      <x:c r="J15" t="inlineStr">
+      <x:c r="I16"/>
+      <x:c r="J16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4</x:t>
         </x:is>
       </x:c>
-      <x:c r="K15" t="inlineStr">
+      <x:c r="K16" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">材质</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="H16" t="inlineStr">
+      <x:c r="L16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17"/>
+      <x:c r="B17"/>
+      <x:c r="C17"/>
+      <x:c r="D17"/>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
+      <x:c r="G17"/>
+      <x:c r="H17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">FlavorSlot</x:t>
         </x:is>
       </x:c>
-      <x:c r="J16" t="inlineStr">
+      <x:c r="I17"/>
+      <x:c r="J17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">5</x:t>
         </x:is>
       </x:c>
-      <x:c r="K16" t="inlineStr">
+      <x:c r="K17" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">某道菜的风味槽</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="H17" t="inlineStr">
+      <x:c r="L17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
+      <x:c r="G18"/>
+      <x:c r="H18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Global</x:t>
         </x:is>
       </x:c>
-      <x:c r="J17" t="inlineStr">
+      <x:c r="I18"/>
+      <x:c r="J18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">6</x:t>
         </x:is>
       </x:c>
-      <x:c r="K17" t="inlineStr">
+      <x:c r="K18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">无目标(全局资源/节奏,时间轴类限地图)</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="B18" t="inlineStr">
+      <x:c r="L18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ItemSpecialTag</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" t="inlineStr">
+      <x:c r="C19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="D18" t="inlineStr">
+      <x:c r="D19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">False</x:t>
         </x:is>
       </x:c>
-      <x:c r="F18" t="str">
+      <x:c r="E19"/>
+      <x:c r="F19" t="str">
         <x:v>装饰品和消耗品特殊标签</x:v>
       </x:c>
-      <x:c r="H18" t="inlineStr">
+      <x:c r="G19"/>
+      <x:c r="H19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="J18" t="n">
+      <x:c r="I19"/>
+      <x:c r="J19" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" t="inlineStr">
+      <x:c r="K19" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">无</x:t>
         </x:is>
       </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="H19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Negative</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K19" t="str">
-        <x:v>诅咒装饰品</x:v>
-      </x:c>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
-      <x:c r="B20" t="str">
-        <x:v>ActiveItemCategory</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>False</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>False</x:v>
-      </x:c>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
       <x:c r="E20"/>
-      <x:c r="F20" t="str">
-        <x:v>消耗品分类</x:v>
-      </x:c>
+      <x:c r="F20"/>
       <x:c r="G20"/>
-      <x:c r="H20" t="str">
-        <x:v>Strengthen</x:v>
+      <x:c r="H20" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Negative</x:t>
+        </x:is>
       </x:c>
       <x:c r="I20"/>
       <x:c r="J20" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>强化类消耗品</x:v>
+        <x:v>诅咒装饰品</x:v>
       </x:c>
       <x:c r="L20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
-      <x:c r="B21"/>
-      <x:c r="C21"/>
-      <x:c r="D21"/>
+      <x:c r="B21" t="str">
+        <x:v>ActiveItemCategory</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>False</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>False</x:v>
+      </x:c>
       <x:c r="E21"/>
-      <x:c r="F21"/>
+      <x:c r="F21" t="str">
+        <x:v>消耗品分类</x:v>
+      </x:c>
       <x:c r="G21"/>
       <x:c r="H21" t="str">
-        <x:v>Adjust</x:v>
+        <x:v>Strengthen</x:v>
       </x:c>
       <x:c r="I21"/>
       <x:c r="J21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>强化类消耗品</x:v>
+      </x:c>
+      <x:c r="L21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+      <x:c r="G22"/>
+      <x:c r="H22" t="str">
+        <x:v>Adjust</x:v>
+      </x:c>
+      <x:c r="I22"/>
+      <x:c r="J22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K21" t="str">
+      <x:c r="K22" t="str">
         <x:v>调整类消耗品</x:v>
       </x:c>
-      <x:c r="L21"/>
+      <x:c r="L22"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
